--- a/public/example/usage-import.xlsx
+++ b/public/example/usage-import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taibif/Documents/00-GitHub/taicol-2021/public/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AB5CCA-22B3-4E47-931E-07520880B271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D3ACAF-DD77-9E4E-83A2-CF5379358EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15760" xr2:uid="{5E2458F6-5B21-7645-B9CB-A68269CDEE8D}"/>
+    <workbookView xWindow="3160" yWindow="22100" windowWidth="28800" windowHeight="15700" xr2:uid="{5E2458F6-5B21-7645-B9CB-A68269CDEE8D}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>rank</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -93,15 +93,87 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>common_name(language,area)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>alien_status_note</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>is_new_record</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>indications</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>usage_references</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>diagnosis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>distribution</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etymology</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>habitat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>substrata</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>measurements</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>coloration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>other_examined_material</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>note</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>common_name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom_field1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom_field2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom_field3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom_field4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>custom_field5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -109,7 +181,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -147,6 +219,28 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -165,12 +259,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -179,8 +274,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Normal_Sheet1_Clements 6.4" xfId="1" xr:uid="{D5CBAE4F-439F-9A4D-BB43-6F4E34FE1CA3}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -493,16 +593,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24BD2BA-B27D-A54D-8E83-71A630B651AD}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="28.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1">
+    <row r="1" spans="1:38" s="2" customFormat="1" ht="13">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -528,41 +631,105 @@
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="X1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/public/example/usage-import.xlsx
+++ b/public/example/usage-import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taibif/Documents/00-GitHub/taicol-2021/public/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D3ACAF-DD77-9E4E-83A2-CF5379358EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630F3DBC-F46D-BB4B-ABA0-4E87C63E5027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3160" yWindow="22100" windowWidth="28800" windowHeight="15700" xr2:uid="{5E2458F6-5B21-7645-B9CB-A68269CDEE8D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>rank</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -106,10 +106,6 @@
   </si>
   <si>
     <t>usage_references</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -593,19 +589,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24BD2BA-B27D-A54D-8E83-71A630B651AD}">
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="28.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="2" customFormat="1" ht="13">
+    <row r="1" spans="1:37" s="2" customFormat="1" ht="13">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -637,43 +633,43 @@
         <v>20</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>22</v>
@@ -700,7 +696,7 @@
         <v>29</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG1" s="2" t="s">
         <v>33</v>
@@ -708,20 +704,17 @@
       <c r="AH1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AJ1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>31</v>
+      <c r="AK1" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:37">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
